--- a/Models/Свиньи/results/Свиньи - Результаты прогнозов SARIMA средние.xlsx
+++ b/Models/Свиньи/results/Свиньи - Результаты прогнозов SARIMA средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>212.6</v>
+        <v>199.53</v>
       </c>
       <c r="C2" t="n">
-        <v>176.7</v>
+        <v>157.56</v>
       </c>
       <c r="D2" t="n">
-        <v>33.15</v>
+        <v>34.23</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.87</v>
+        <v>10.68</v>
       </c>
       <c r="C3" t="n">
-        <v>18.46</v>
+        <v>9.25</v>
       </c>
       <c r="D3" t="n">
-        <v>23.86</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.45</v>
+        <v>77.3</v>
       </c>
       <c r="C4" t="n">
-        <v>85.03</v>
+        <v>67.11</v>
       </c>
       <c r="D4" t="n">
-        <v>115.71</v>
+        <v>196.48</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.4</v>
+        <v>0.22</v>
       </c>
       <c r="C5" t="n">
-        <v>0.83</v>
+        <v>0.13</v>
       </c>
       <c r="D5" t="n">
-        <v>1.720769583627235e+20</v>
+        <v>1.560150713042329e+20</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>132.36</v>
+        <v>133.94</v>
       </c>
       <c r="C6" t="n">
-        <v>120.34</v>
+        <v>119.29</v>
       </c>
       <c r="D6" t="n">
-        <v>29.98</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="D7" t="n">
-        <v>6.541660546981151e+19</v>
+        <v>4.753769302223073e+18</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         <v>0.02</v>
       </c>
       <c r="D8" t="n">
-        <v>2.911976557526964e+20</v>
+        <v>1.088086260619153e+20</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
       <c r="C9" t="n">
-        <v>0.37</v>
+        <v>0.62</v>
       </c>
       <c r="D9" t="n">
-        <v>9.06</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="C10" t="n">
-        <v>6.7</v>
+        <v>6.87</v>
       </c>
       <c r="D10" t="n">
-        <v>19.91</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.49</v>
+        <v>23.06</v>
       </c>
       <c r="C11" t="n">
-        <v>23.35</v>
+        <v>20.13</v>
       </c>
       <c r="D11" t="n">
-        <v>13.43</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99.26000000000001</v>
+        <v>174.15</v>
       </c>
       <c r="C12" t="n">
-        <v>82.78</v>
+        <v>154.27</v>
       </c>
       <c r="D12" t="n">
-        <v>10.61</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>82.43000000000001</v>
+        <v>112.3</v>
       </c>
       <c r="C13" t="n">
-        <v>73.81999999999999</v>
+        <v>102.88</v>
       </c>
       <c r="D13" t="n">
-        <v>22.32</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.49</v>
+        <v>5.85</v>
       </c>
       <c r="C14" t="n">
-        <v>10.51</v>
+        <v>4.02</v>
       </c>
       <c r="D14" t="n">
-        <v>161.48</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5.941923480432439e+17</v>
+        <v>3.566357919365962e+17</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54.58</v>
+        <v>46.68</v>
       </c>
       <c r="C16" t="n">
-        <v>42.22</v>
+        <v>30.21</v>
       </c>
       <c r="D16" t="n">
-        <v>48.1</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>234.34</v>
+        <v>355.47</v>
       </c>
       <c r="C17" t="n">
-        <v>167.8</v>
+        <v>296.42</v>
       </c>
       <c r="D17" t="n">
-        <v>55.61</v>
+        <v>168.03</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="C18" t="n">
-        <v>0.86</v>
+        <v>1.26</v>
       </c>
       <c r="D18" t="n">
-        <v>8.335332840358918e+22</v>
+        <v>2.304214110064169e+21</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>208.68</v>
+        <v>256.83</v>
       </c>
       <c r="C19" t="n">
-        <v>177.46</v>
+        <v>224.91</v>
       </c>
       <c r="D19" t="n">
-        <v>11.24</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>374.67</v>
+        <v>310.93</v>
       </c>
       <c r="C20" t="n">
-        <v>330.61</v>
+        <v>280.43</v>
       </c>
       <c r="D20" t="n">
-        <v>21.45</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="C21" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="D21" t="n">
-        <v>3.613712429618653e+22</v>
+        <v>71.05</v>
       </c>
     </row>
   </sheetData>
